--- a/artfynd/A 13795-2025 artfynd.xlsx
+++ b/artfynd/A 13795-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124514198</v>
+        <v>124513835</v>
       </c>
       <c r="B2" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,46 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -735,13 +720,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>499451</v>
+        <v>499450</v>
       </c>
       <c r="R2" t="n">
-        <v>7017544</v>
+        <v>7017545</v>
       </c>
       <c r="S2" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -775,7 +760,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Minst 150 plantor och 1 vinterståndare inom ca 2 m2 yta intill en gammal sälg med lunglav som står tätt inpå en gran i gammal barrskog.</t>
+          <t>Ymnig påväxt på en levande sälg och en sälghögstubbe.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,13 +769,32 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -808,7 +812,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124513835</v>
+        <v>124513898</v>
       </c>
       <c r="B3" t="n">
         <v>79891</v>
@@ -853,13 +857,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>499450</v>
+        <v>499443</v>
       </c>
       <c r="R3" t="n">
-        <v>7017545</v>
+        <v>7017543</v>
       </c>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -893,7 +897,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ymnig påväxt på en levande sälg och en sälghögstubbe.</t>
+          <t>Växer ymnigt på flera granar intill gamla sälgar med lunglav.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,27 +911,27 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -945,10 +949,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124513898</v>
+        <v>124514198</v>
       </c>
       <c r="B4" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -957,31 +961,46 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -990,10 +1009,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>499443</v>
+        <v>499451</v>
       </c>
       <c r="R4" t="n">
-        <v>7017543</v>
+        <v>7017544</v>
       </c>
       <c r="S4" t="n">
         <v>12</v>
@@ -1030,7 +1049,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Växer ymnigt på flera granar intill gamla sälgar med lunglav.</t>
+          <t>Minst 150 plantor och 1 vinterståndare inom ca 2 m2 yta intill en gammal sälg med lunglav som står tätt inpå en gran i gammal barrskog.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1039,32 +1058,13 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>

--- a/artfynd/A 13795-2025 artfynd.xlsx
+++ b/artfynd/A 13795-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124513835</v>
+        <v>124514198</v>
       </c>
       <c r="B2" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,46 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,13 +735,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>499450</v>
+        <v>499451</v>
       </c>
       <c r="R2" t="n">
-        <v>7017545</v>
+        <v>7017544</v>
       </c>
       <c r="S2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,7 +775,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ymnig påväxt på en levande sälg och en sälghögstubbe.</t>
+          <t>Minst 150 plantor och 1 vinterståndare inom ca 2 m2 yta intill en gammal sälg med lunglav som står tätt inpå en gran i gammal barrskog.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,32 +784,13 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -812,7 +808,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124513898</v>
+        <v>124513835</v>
       </c>
       <c r="B3" t="n">
         <v>79891</v>
@@ -857,13 +853,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>499443</v>
+        <v>499450</v>
       </c>
       <c r="R3" t="n">
-        <v>7017543</v>
+        <v>7017545</v>
       </c>
       <c r="S3" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -897,7 +893,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Växer ymnigt på flera granar intill gamla sälgar med lunglav.</t>
+          <t>Ymnig påväxt på en levande sälg och en sälghögstubbe.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -911,27 +907,27 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -949,10 +945,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124514198</v>
+        <v>124513898</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -961,46 +957,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -1009,10 +990,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>499451</v>
+        <v>499443</v>
       </c>
       <c r="R4" t="n">
-        <v>7017544</v>
+        <v>7017543</v>
       </c>
       <c r="S4" t="n">
         <v>12</v>
@@ -1049,7 +1030,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Minst 150 plantor och 1 vinterståndare inom ca 2 m2 yta intill en gammal sälg med lunglav som står tätt inpå en gran i gammal barrskog.</t>
+          <t>Växer ymnigt på flera granar intill gamla sälgar med lunglav.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1058,13 +1039,32 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>

--- a/artfynd/A 13795-2025 artfynd.xlsx
+++ b/artfynd/A 13795-2025 artfynd.xlsx
@@ -812,10 +812,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124513898</v>
+        <v>124514198</v>
       </c>
       <c r="B3" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -824,31 +824,46 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -857,10 +872,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>499443</v>
+        <v>499451</v>
       </c>
       <c r="R3" t="n">
-        <v>7017543</v>
+        <v>7017544</v>
       </c>
       <c r="S3" t="n">
         <v>12</v>
@@ -897,7 +912,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Växer ymnigt på flera granar intill gamla sälgar med lunglav.</t>
+          <t>Minst 150 plantor och 1 vinterståndare inom ca 2 m2 yta intill en gammal sälg med lunglav som står tätt inpå en gran i gammal barrskog.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,32 +921,13 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -949,10 +945,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124514198</v>
+        <v>124513898</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -961,46 +957,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -1009,10 +990,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>499451</v>
+        <v>499443</v>
       </c>
       <c r="R4" t="n">
-        <v>7017544</v>
+        <v>7017543</v>
       </c>
       <c r="S4" t="n">
         <v>12</v>
@@ -1049,7 +1030,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Minst 150 plantor och 1 vinterståndare inom ca 2 m2 yta intill en gammal sälg med lunglav som står tätt inpå en gran i gammal barrskog.</t>
+          <t>Växer ymnigt på flera granar intill gamla sälgar med lunglav.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1058,13 +1039,32 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>

--- a/artfynd/A 13795-2025 artfynd.xlsx
+++ b/artfynd/A 13795-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124513835</v>
+        <v>124514198</v>
       </c>
       <c r="B2" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,46 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,13 +735,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>499450</v>
+        <v>499451</v>
       </c>
       <c r="R2" t="n">
-        <v>7017545</v>
+        <v>7017544</v>
       </c>
       <c r="S2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,7 +775,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ymnig påväxt på en levande sälg och en sälghögstubbe.</t>
+          <t>Minst 150 plantor och 1 vinterståndare inom ca 2 m2 yta intill en gammal sälg med lunglav som står tätt inpå en gran i gammal barrskog.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,32 +784,13 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -812,10 +808,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124514198</v>
+        <v>124513835</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -824,46 +820,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -872,13 +853,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>499451</v>
+        <v>499450</v>
       </c>
       <c r="R3" t="n">
-        <v>7017544</v>
+        <v>7017545</v>
       </c>
       <c r="S3" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -912,7 +893,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Minst 150 plantor och 1 vinterståndare inom ca 2 m2 yta intill en gammal sälg med lunglav som står tätt inpå en gran i gammal barrskog.</t>
+          <t>Ymnig påväxt på en levande sälg och en sälghögstubbe.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -921,13 +902,32 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>

--- a/artfynd/A 13795-2025 artfynd.xlsx
+++ b/artfynd/A 13795-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124513835</v>
+        <v>124514198</v>
       </c>
       <c r="B2" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,46 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,13 +735,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>499450</v>
+        <v>499451</v>
       </c>
       <c r="R2" t="n">
-        <v>7017545</v>
+        <v>7017544</v>
       </c>
       <c r="S2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,7 +775,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ymnig påväxt på en levande sälg och en sälghögstubbe.</t>
+          <t>Minst 150 plantor och 1 vinterståndare inom ca 2 m2 yta intill en gammal sälg med lunglav som står tätt inpå en gran i gammal barrskog.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,32 +784,13 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -949,10 +945,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124514198</v>
+        <v>124513835</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -961,46 +957,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -1009,13 +990,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>499451</v>
+        <v>499450</v>
       </c>
       <c r="R4" t="n">
-        <v>7017544</v>
+        <v>7017545</v>
       </c>
       <c r="S4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1049,7 +1030,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Minst 150 plantor och 1 vinterståndare inom ca 2 m2 yta intill en gammal sälg med lunglav som står tätt inpå en gran i gammal barrskog.</t>
+          <t>Ymnig påväxt på en levande sälg och en sälghögstubbe.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1058,13 +1039,32 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>

--- a/artfynd/A 13795-2025 artfynd.xlsx
+++ b/artfynd/A 13795-2025 artfynd.xlsx
@@ -808,7 +808,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124513898</v>
+        <v>124513835</v>
       </c>
       <c r="B3" t="n">
         <v>79891</v>
@@ -853,13 +853,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>499443</v>
+        <v>499450</v>
       </c>
       <c r="R3" t="n">
-        <v>7017543</v>
+        <v>7017545</v>
       </c>
       <c r="S3" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Växer ymnigt på flera granar intill gamla sälgar med lunglav.</t>
+          <t>Ymnig påväxt på en levande sälg och en sälghögstubbe.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,27 +907,27 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -945,7 +945,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124513835</v>
+        <v>124513898</v>
       </c>
       <c r="B4" t="n">
         <v>79891</v>
@@ -990,13 +990,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>499450</v>
+        <v>499443</v>
       </c>
       <c r="R4" t="n">
-        <v>7017545</v>
+        <v>7017543</v>
       </c>
       <c r="S4" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ymnig påväxt på en levande sälg och en sälghögstubbe.</t>
+          <t>Växer ymnigt på flera granar intill gamla sälgar med lunglav.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1044,27 +1044,27 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>

--- a/artfynd/A 13795-2025 artfynd.xlsx
+++ b/artfynd/A 13795-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124513835</v>
+        <v>124514198</v>
       </c>
       <c r="B2" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,46 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,13 +735,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>499450</v>
+        <v>499451</v>
       </c>
       <c r="R2" t="n">
-        <v>7017545</v>
+        <v>7017544</v>
       </c>
       <c r="S2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,7 +775,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ymnig påväxt på en levande sälg och en sälghögstubbe.</t>
+          <t>Minst 150 plantor och 1 vinterståndare inom ca 2 m2 yta intill en gammal sälg med lunglav som står tätt inpå en gran i gammal barrskog.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,32 +784,13 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -812,10 +808,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124514198</v>
+        <v>124513898</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -824,46 +820,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -872,10 +853,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>499451</v>
+        <v>499443</v>
       </c>
       <c r="R3" t="n">
-        <v>7017544</v>
+        <v>7017543</v>
       </c>
       <c r="S3" t="n">
         <v>12</v>
@@ -912,7 +893,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Minst 150 plantor och 1 vinterståndare inom ca 2 m2 yta intill en gammal sälg med lunglav som står tätt inpå en gran i gammal barrskog.</t>
+          <t>Växer ymnigt på flera granar intill gamla sälgar med lunglav.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -921,13 +902,32 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -945,7 +945,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124513898</v>
+        <v>124513835</v>
       </c>
       <c r="B4" t="n">
         <v>79891</v>
@@ -990,13 +990,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>499443</v>
+        <v>499450</v>
       </c>
       <c r="R4" t="n">
-        <v>7017543</v>
+        <v>7017545</v>
       </c>
       <c r="S4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Växer ymnigt på flera granar intill gamla sälgar med lunglav.</t>
+          <t>Ymnig påväxt på en levande sälg och en sälghögstubbe.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1044,27 +1044,27 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>

--- a/artfynd/A 13795-2025 artfynd.xlsx
+++ b/artfynd/A 13795-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,58 +675,38 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124514198</v>
+        <v>124513835</v>
       </c>
       <c r="B2" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -735,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>499451</v>
+        <v>499450</v>
       </c>
       <c r="R2" t="n">
-        <v>7017544</v>
+        <v>7017545</v>
       </c>
       <c r="S2" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -775,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Minst 150 plantor och 1 vinterståndare inom ca 2 m2 yta intill en gammal sälg med lunglav som står tätt inpå en gran i gammal barrskog.</t>
+          <t>Ymnig påväxt på en levande sälg och en sälghögstubbe.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,13 +764,32 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -811,12 +810,7 @@
         <v>124513898</v>
       </c>
       <c r="B3" t="n">
-        <v>79891</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -945,15 +939,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124513835</v>
+        <v>124514313</v>
       </c>
       <c r="B4" t="n">
-        <v>79891</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57364</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -961,27 +950,36 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>102954</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>med soral</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -990,13 +988,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>499450</v>
+        <v>499470</v>
       </c>
       <c r="R4" t="n">
-        <v>7017545</v>
+        <v>7017530</v>
       </c>
       <c r="S4" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1026,11 +1024,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ymnig påväxt på en levande sälg och en sälghögstubbe.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1042,31 +1035,6 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
-      </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
@@ -1079,6 +1047,134 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>124514198</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Igeltjärnen, Igeltjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>499451</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7017544</v>
+      </c>
+      <c r="S5" t="n">
+        <v>12</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Minst 150 plantor och 1 vinterståndare inom ca 2 m2 yta intill en gammal sälg med lunglav som står tätt inpå en gran i gammal barrskog.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 13795-2025 artfynd.xlsx
+++ b/artfynd/A 13795-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -804,6 +809,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124513835</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -936,6 +946,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124513898</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1047,6 +1062,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124514313</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1175,8 +1195,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124514198</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>